--- a/data/nzd0193/nzd0193.xlsx
+++ b/data/nzd0193/nzd0193.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E667"/>
+  <dimension ref="A1:E673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14439,6 +14439,132 @@
         <v>372.01</v>
       </c>
       <c r="E667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>355.96</v>
+      </c>
+      <c r="C668" t="n">
+        <v>354.8</v>
+      </c>
+      <c r="D668" t="n">
+        <v>371</v>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>356.01</v>
+      </c>
+      <c r="C669" t="n">
+        <v>355.44</v>
+      </c>
+      <c r="D669" t="n">
+        <v>371.07</v>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>354.54</v>
+      </c>
+      <c r="C670" t="n">
+        <v>355.37</v>
+      </c>
+      <c r="D670" t="n">
+        <v>370.37</v>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:16+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>354.7</v>
+      </c>
+      <c r="C671" t="n">
+        <v>356.04</v>
+      </c>
+      <c r="D671" t="n">
+        <v>370.37</v>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>355.26</v>
+      </c>
+      <c r="C672" t="n">
+        <v>356.96</v>
+      </c>
+      <c r="D672" t="n">
+        <v>370.37</v>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>355.37</v>
+      </c>
+      <c r="C673" t="n">
+        <v>357.48</v>
+      </c>
+      <c r="D673" t="n">
+        <v>370.62</v>
+      </c>
+      <c r="E673" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14455,7 +14581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B778"/>
+  <dimension ref="A1:B784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22238,6 +22364,66 @@
       </c>
       <c r="B778" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-06-27 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B779" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B780" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B781" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B782" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B783" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B784" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -22406,28 +22592,28 @@
         <v>0.0914</v>
       </c>
       <c r="I2" t="n">
-        <v>0.283268765954221</v>
+        <v>0.2785070217287618</v>
       </c>
       <c r="J2" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="K2" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08841184510433486</v>
+        <v>0.08701042038925666</v>
       </c>
       <c r="M2" t="n">
-        <v>5.581685796659177</v>
+        <v>5.558814371951486</v>
       </c>
       <c r="N2" t="n">
-        <v>48.98356988085193</v>
+        <v>48.62364943040861</v>
       </c>
       <c r="O2" t="n">
-        <v>6.998826321666507</v>
+        <v>6.973065999286728</v>
       </c>
       <c r="P2" t="n">
-        <v>350.5918741571605</v>
+        <v>350.642440843347</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22484,28 +22670,28 @@
         <v>0.0677</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4243267678223551</v>
+        <v>0.4208515558920762</v>
       </c>
       <c r="J3" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="K3" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1657886078314201</v>
+        <v>0.1658778890130004</v>
       </c>
       <c r="M3" t="n">
-        <v>5.884714197130006</v>
+        <v>5.850866548016741</v>
       </c>
       <c r="N3" t="n">
-        <v>53.63979665065459</v>
+        <v>53.20833970989859</v>
       </c>
       <c r="O3" t="n">
-        <v>7.323919486904167</v>
+        <v>7.294404685092443</v>
       </c>
       <c r="P3" t="n">
-        <v>346.7051365382858</v>
+        <v>346.7420169020862</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22562,28 +22748,28 @@
         <v>0.1102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5050277688633811</v>
+        <v>0.4820617950470769</v>
       </c>
       <c r="J4" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="K4" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0303009347772325</v>
+        <v>0.0280715829706617</v>
       </c>
       <c r="M4" t="n">
-        <v>17.49925778706056</v>
+        <v>17.45133484749055</v>
       </c>
       <c r="N4" t="n">
-        <v>483.2549371879931</v>
+        <v>480.6771787302608</v>
       </c>
       <c r="O4" t="n">
-        <v>21.98306023255163</v>
+        <v>21.92435127273464</v>
       </c>
       <c r="P4" t="n">
-        <v>371.1367725951406</v>
+        <v>371.3806328331711</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22621,7 +22807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E667"/>
+  <dimension ref="A1:E673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40633,6 +40819,168 @@
         </is>
       </c>
     </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>-37.16590033933489,175.88151154578202</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>-37.16661493303371,175.88157055168645</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>-37.16731391953651,175.88182396273993</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>-37.16590029440376,175.88151210569507</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>-37.16661435791082,175.88157771864044</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>-37.16731385663071,175.88182474663245</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>-37.16590161537788,175.8814956442506</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>-37.1666144208149,175.88157693475483</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>-37.16731448568832,175.8818169077074</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:16+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>-37.16590147159849,175.88149743597248</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>-37.16661381873271,175.88158443765968</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>-37.16731448568832,175.8818169077074</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>-37.165900968370416,175.881503706999</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>-37.16661299199222,175.8815947401556</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>-37.16731448568832,175.8818169077074</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>-37.16590086952202,175.88150493880778</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>-37.166612524703716,175.88160056330534</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>-37.167314261024956,175.8818197073235</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0193/nzd0193.xlsx
+++ b/data/nzd0193/nzd0193.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E673"/>
+  <dimension ref="A1:E678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14565,6 +14565,111 @@
         <v>370.62</v>
       </c>
       <c r="E673" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:27+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>355.99</v>
+      </c>
+      <c r="C674" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="D674" t="n">
+        <v>373.27</v>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>357.24</v>
+      </c>
+      <c r="C675" t="n">
+        <v>359.24</v>
+      </c>
+      <c r="D675" t="n">
+        <v>376.99</v>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>358.14</v>
+      </c>
+      <c r="C676" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="D676" t="n">
+        <v>381.89</v>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>359.07</v>
+      </c>
+      <c r="C677" t="n">
+        <v>360.99</v>
+      </c>
+      <c r="D677" t="n">
+        <v>382.82</v>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>359.01</v>
+      </c>
+      <c r="C678" t="n">
+        <v>361.47</v>
+      </c>
+      <c r="D678" t="n">
+        <v>382.16</v>
+      </c>
+      <c r="E678" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14581,7 +14686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B784"/>
+  <dimension ref="A1:B789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22424,6 +22529,56 @@
       </c>
       <c r="B784" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B785" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B786" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B787" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B788" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B789" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -22592,28 +22747,28 @@
         <v>0.0914</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2785070217287618</v>
+        <v>0.2781218256095402</v>
       </c>
       <c r="J2" t="n">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="K2" t="n">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08701042038925666</v>
+        <v>0.08794805306653053</v>
       </c>
       <c r="M2" t="n">
-        <v>5.558814371951486</v>
+        <v>5.524974230755677</v>
       </c>
       <c r="N2" t="n">
-        <v>48.62364943040861</v>
+        <v>48.27496261855855</v>
       </c>
       <c r="O2" t="n">
-        <v>6.973065999286728</v>
+        <v>6.948018610982454</v>
       </c>
       <c r="P2" t="n">
-        <v>350.642440843347</v>
+        <v>350.6465248313739</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22670,28 +22825,28 @@
         <v>0.0677</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4208515558920762</v>
+        <v>0.4233190633725386</v>
       </c>
       <c r="J3" t="n">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="K3" t="n">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1658778890130004</v>
+        <v>0.1694736138324925</v>
       </c>
       <c r="M3" t="n">
-        <v>5.850866548016741</v>
+        <v>5.821270435562948</v>
       </c>
       <c r="N3" t="n">
-        <v>53.20833970989859</v>
+        <v>52.85005647018397</v>
       </c>
       <c r="O3" t="n">
-        <v>7.294404685092443</v>
+        <v>7.26980443135742</v>
       </c>
       <c r="P3" t="n">
-        <v>346.7420169020862</v>
+        <v>346.7156885979648</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22748,28 +22903,28 @@
         <v>0.1102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4820617950470769</v>
+        <v>0.4753929305775235</v>
       </c>
       <c r="J4" t="n">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="K4" t="n">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0280715829706617</v>
+        <v>0.02769960895919843</v>
       </c>
       <c r="M4" t="n">
-        <v>17.45133484749055</v>
+        <v>17.35396556287318</v>
       </c>
       <c r="N4" t="n">
-        <v>480.6771787302608</v>
+        <v>477.4091286085819</v>
       </c>
       <c r="O4" t="n">
-        <v>21.92435127273464</v>
+        <v>21.84969401636054</v>
       </c>
       <c r="P4" t="n">
-        <v>371.3806328331711</v>
+        <v>371.4516620696622</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22807,7 +22962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E673"/>
+  <dimension ref="A1:E678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40981,6 +41136,141 @@
         </is>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:27+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>-37.16590031237622,175.88151188172986</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>-37.16661187768841,175.8816086261279</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>-37.167311879589164,175.88184938325298</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>-37.16589918909715,175.88152587955622</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>-37.166610943109774,175.88162027242686</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>-37.16730853658009,175.88189104153494</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>-37.16589838033522,175.88153595799088</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>-37.16661026913409,175.88162867119993</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>-37.16730413313199,175.88194591399602</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>-37.16589754461366,175.8815463723731</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>-37.16660937049893,175.88163986956374</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>-37.167303297372676,175.88195632856429</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>-37.1658975985312,175.88154570047746</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>-37.16660893915369,175.88164524477824</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>-37.16730389049229,175.8819489375804</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0193/nzd0193.xlsx
+++ b/data/nzd0193/nzd0193.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E678"/>
+  <dimension ref="A1:E681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14646,7 +14646,7 @@
         <v>360.99</v>
       </c>
       <c r="D677" t="n">
-        <v>382.82</v>
+        <v>382.77</v>
       </c>
       <c r="E677" t="inlineStr">
         <is>
@@ -14667,9 +14667,72 @@
         <v>361.47</v>
       </c>
       <c r="D678" t="n">
-        <v>382.16</v>
+        <v>383.6</v>
       </c>
       <c r="E678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>359.25</v>
+      </c>
+      <c r="C679" t="n">
+        <v>361.57</v>
+      </c>
+      <c r="D679" t="n">
+        <v>386.59</v>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>358.86</v>
+      </c>
+      <c r="C680" t="n">
+        <v>361.92</v>
+      </c>
+      <c r="D680" t="n">
+        <v>387.73</v>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>359.26</v>
+      </c>
+      <c r="C681" t="n">
+        <v>362.2</v>
+      </c>
+      <c r="D681" t="n">
+        <v>387.57</v>
+      </c>
+      <c r="E681" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14686,7 +14749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B789"/>
+  <dimension ref="A1:B792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22579,6 +22642,36 @@
       </c>
       <c r="B789" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B790" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B791" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B792" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -22747,28 +22840,28 @@
         <v>0.0914</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2781218256095402</v>
+        <v>0.2788558904602103</v>
       </c>
       <c r="J2" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="K2" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08794805306653053</v>
+        <v>0.08907515642575758</v>
       </c>
       <c r="M2" t="n">
-        <v>5.524974230755677</v>
+        <v>5.504506932261386</v>
       </c>
       <c r="N2" t="n">
-        <v>48.27496261855855</v>
+        <v>48.06582950633296</v>
       </c>
       <c r="O2" t="n">
-        <v>6.948018610982454</v>
+        <v>6.932952437910775</v>
       </c>
       <c r="P2" t="n">
-        <v>350.6465248313739</v>
+        <v>350.638665285121</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22825,28 +22918,28 @@
         <v>0.0677</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4233190633725386</v>
+        <v>0.4262552804905027</v>
       </c>
       <c r="J3" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="K3" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1694736138324925</v>
+        <v>0.1725178827336993</v>
       </c>
       <c r="M3" t="n">
-        <v>5.821270435562948</v>
+        <v>5.81176303517071</v>
       </c>
       <c r="N3" t="n">
-        <v>52.85005647018397</v>
+        <v>52.67625418972604</v>
       </c>
       <c r="O3" t="n">
-        <v>7.26980443135742</v>
+        <v>7.257840876577968</v>
       </c>
       <c r="P3" t="n">
-        <v>346.7156885979648</v>
+        <v>346.6842494820914</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22903,28 +22996,28 @@
         <v>0.1102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4753929305775235</v>
+        <v>0.4781024779795259</v>
       </c>
       <c r="J4" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="K4" t="n">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02769960895919843</v>
+        <v>0.0282455007263267</v>
       </c>
       <c r="M4" t="n">
-        <v>17.35396556287318</v>
+        <v>17.29027118486284</v>
       </c>
       <c r="N4" t="n">
-        <v>477.4091286085819</v>
+        <v>475.3353509264151</v>
       </c>
       <c r="O4" t="n">
-        <v>21.84969401636054</v>
+        <v>21.80218683816867</v>
       </c>
       <c r="P4" t="n">
-        <v>371.4516620696622</v>
+        <v>371.4226574167832</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22962,7 +23055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E678"/>
+  <dimension ref="A1:E681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41235,7 +41328,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>-37.167303297372676,175.88195632856429</t>
+          <t>-37.167303342306,175.88195576864126</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -41262,10 +41355,91 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>-37.16730389049229,175.8819489375804</t>
+          <t>-37.167302596412554,175.88196506336322</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>-37.16589738286098,175.8815483880599</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>-37.16660884929007,175.8816463646146</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>-37.16729990939284,175.88199854675727</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>-37.165897733325046,175.8815440207384</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>-37.166608534767306,175.88165028404177</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>-37.16729888490792,175.8820113130004</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>-37.16589737387472,175.88154850004253</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>-37.166608283148996,175.88165341958347</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>-37.16729902869536,175.882009521247</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
